--- a/DataframeAcoes.xlsx
+++ b/DataframeAcoes.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataframeAcoes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataframeAcoes_Variacao" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,10 +438,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>103.68</v>
+        <v>103.3</v>
       </c>
       <c r="C2" t="n">
-        <v>159.08</v>
+        <v>157.41</v>
       </c>
     </row>
     <row r="3">
@@ -449,10 +449,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>105.82</v>
+        <v>103.33</v>
       </c>
       <c r="C3" t="n">
-        <v>155.17</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="4">
@@ -460,10 +460,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>106.28</v>
+        <v>107.91</v>
       </c>
       <c r="C4" t="n">
-        <v>152.02</v>
+        <v>156.7</v>
       </c>
     </row>
     <row r="5">
@@ -471,7 +471,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>106.49</v>
+        <v>110.17</v>
       </c>
       <c r="C5" t="n">
         <v>150.69</v>
@@ -482,10 +482,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>108.08</v>
+        <v>108.23</v>
       </c>
       <c r="C6" t="n">
-        <v>150.57</v>
+        <v>148.08</v>
       </c>
     </row>
     <row r="7">
@@ -493,10 +493,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>111.44</v>
+        <v>107.59</v>
       </c>
       <c r="C7" t="n">
-        <v>149.92</v>
+        <v>149.05</v>
       </c>
     </row>
     <row r="8">
@@ -504,10 +504,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>115.31</v>
+        <v>106.96</v>
       </c>
       <c r="C8" t="n">
-        <v>147.51</v>
+        <v>145.82</v>
       </c>
     </row>
     <row r="9">
@@ -515,10 +515,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>117.98</v>
+        <v>111.39</v>
       </c>
       <c r="C9" t="n">
-        <v>143.71</v>
+        <v>146.96</v>
       </c>
     </row>
     <row r="10">
@@ -526,10 +526,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>118.82</v>
+        <v>109.87</v>
       </c>
       <c r="C10" t="n">
-        <v>140.18</v>
+        <v>146.61</v>
       </c>
     </row>
     <row r="11">
@@ -537,10 +537,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>118.91</v>
+        <v>114.94</v>
       </c>
       <c r="C11" t="n">
-        <v>138.32</v>
+        <v>142.61</v>
       </c>
     </row>
     <row r="12">
@@ -548,10 +548,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>120</v>
+        <v>116.92</v>
       </c>
       <c r="C12" t="n">
-        <v>138.01</v>
+        <v>146.11</v>
       </c>
     </row>
     <row r="13">
@@ -559,10 +559,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>122.93</v>
+        <v>116.48</v>
       </c>
       <c r="C13" t="n">
-        <v>137.69</v>
+        <v>141.85</v>
       </c>
     </row>
     <row r="14">
@@ -570,10 +570,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>126.84</v>
+        <v>122.67</v>
       </c>
       <c r="C14" t="n">
-        <v>135.81</v>
+        <v>141.47</v>
       </c>
     </row>
     <row r="15">
@@ -581,10 +581,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>129.98</v>
+        <v>119.87</v>
       </c>
       <c r="C15" t="n">
-        <v>132.27</v>
+        <v>138.09</v>
       </c>
     </row>
     <row r="16">
@@ -592,10 +592,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>131.3</v>
+        <v>126.46</v>
       </c>
       <c r="C16" t="n">
-        <v>128.48</v>
+        <v>138.82</v>
       </c>
     </row>
     <row r="17">
@@ -603,10 +603,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>131.42</v>
+        <v>127.82</v>
       </c>
       <c r="C17" t="n">
-        <v>126.08</v>
+        <v>137.09</v>
       </c>
     </row>
     <row r="18">
@@ -614,10 +614,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>132.08</v>
+        <v>127.31</v>
       </c>
       <c r="C18" t="n">
-        <v>125.45</v>
+        <v>136.13</v>
       </c>
     </row>
     <row r="19">
@@ -625,10 +625,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>134.5</v>
+        <v>127.1</v>
       </c>
       <c r="C19" t="n">
-        <v>125.32</v>
+        <v>131.49</v>
       </c>
     </row>
     <row r="20">
@@ -636,10 +636,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>138.3</v>
+        <v>130.33</v>
       </c>
       <c r="C20" t="n">
-        <v>123.98</v>
+        <v>130.22</v>
       </c>
     </row>
     <row r="21">
@@ -647,10 +647,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>141.83</v>
+        <v>131.08</v>
       </c>
       <c r="C21" t="n">
-        <v>120.82</v>
+        <v>128.79</v>
       </c>
     </row>
     <row r="22">
@@ -658,10 +658,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>143.67</v>
+        <v>130.97</v>
       </c>
       <c r="C22" t="n">
-        <v>116.9</v>
+        <v>124.82</v>
       </c>
     </row>
     <row r="23">
@@ -669,10 +669,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>143.98</v>
+        <v>129.37</v>
       </c>
       <c r="C23" t="n">
-        <v>114</v>
+        <v>125.75</v>
       </c>
     </row>
     <row r="24">
@@ -680,10 +680,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>144.31</v>
+        <v>130.23</v>
       </c>
       <c r="C24" t="n">
-        <v>112.93</v>
+        <v>124.86</v>
       </c>
     </row>
     <row r="25">
@@ -691,10 +691,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>146.19</v>
+        <v>132.53</v>
       </c>
       <c r="C25" t="n">
-        <v>112.85</v>
+        <v>124.36</v>
       </c>
     </row>
     <row r="26">
@@ -702,10 +702,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>149.74</v>
+        <v>138.18</v>
       </c>
       <c r="C26" t="n">
-        <v>111.98</v>
+        <v>123.68</v>
       </c>
     </row>
     <row r="27">
@@ -713,10 +713,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>153.53</v>
+        <v>139.06</v>
       </c>
       <c r="C27" t="n">
-        <v>109.29</v>
+        <v>121.07</v>
       </c>
     </row>
     <row r="28">
@@ -724,10 +724,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>155.91</v>
+        <v>140.71</v>
       </c>
       <c r="C28" t="n">
-        <v>105.42</v>
+        <v>123.31</v>
       </c>
     </row>
     <row r="29">
@@ -735,10 +735,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>156.54</v>
+        <v>144.87</v>
       </c>
       <c r="C29" t="n">
-        <v>102.07</v>
+        <v>118.93</v>
       </c>
     </row>
     <row r="30">
@@ -746,10 +746,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>156.67</v>
+        <v>143.4</v>
       </c>
       <c r="C30" t="n">
-        <v>100.5</v>
+        <v>117.16</v>
       </c>
     </row>
     <row r="31">
@@ -757,10 +757,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>158.02</v>
+        <v>144.28</v>
       </c>
       <c r="C31" t="n">
-        <v>100.31</v>
+        <v>112.76</v>
       </c>
     </row>
   </sheetData>
